--- a/Luban/Config/Datas/EnemyData.xlsx
+++ b/Luban/Config/Datas/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="2"/>
@@ -7912,6 +7912,210 @@
       <c r="P131" s="0" t="inlineStr">
         <is>
           <t>挑战档：Scorpions / small</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t>RatKing</t>
+        </is>
+      </c>
+      <c r="F132" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G132" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_RatKing</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J132" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="K132" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L132" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M132" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="0" t="inlineStr"/>
+      <c r="P132" s="0" t="inlineStr">
+        <is>
+          <t>Boss 1：鼠王。首个真正的 Boss 行（type=5），血厚、带护甲、漏了扣 5 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t>BugQueen</t>
+        </is>
+      </c>
+      <c r="F133" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G133" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_BugQueen</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J133" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="K133" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="L133" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M133" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="0" t="inlineStr"/>
+      <c r="P133" s="0" t="inlineStr">
+        <is>
+          <t>Boss 2：虫后。护甲 0.45，必须靠高单发伤害（强力塔/激光塔）才打得动</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="0" t="n">
+        <v>131</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t>MossQueen</t>
+        </is>
+      </c>
+      <c r="F134" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H134" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_MossQueen</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J134" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="K134" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L134" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M134" s="0" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="0" t="inlineStr"/>
+      <c r="P134" s="0" t="inlineStr">
+        <is>
+          <t>Boss 3：苔藓女王。终盘 Boss，护甲 0.5 使纯靠数量的小塔几乎无效</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t>Ironclad</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G135" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_Dreadnought</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J135" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="K135" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L135" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M135" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="0" t="inlineStr"/>
+      <c r="P135" s="0" t="inlineStr">
+        <is>
+          <t>高护甲精英：护甲 0.65 是当前全表最高档，专门用来验证护甲减伤链路</t>
         </is>
       </c>
     </row>
